--- a/artfynd/A 41846-2026 artfynd.xlsx
+++ b/artfynd/A 41846-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137498796</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137498806</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137498809</v>
       </c>
       <c r="B4" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137498795</v>
       </c>
       <c r="B5" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137498794</v>
       </c>
       <c r="B6" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137498807</v>
       </c>
       <c r="B7" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137498810</v>
       </c>
       <c r="B8" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137498790</v>
       </c>
       <c r="B9" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137498805</v>
       </c>
       <c r="B10" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137498788</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137498792</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137498793</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137498797</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137498799</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>137498798</v>
       </c>
       <c r="B16" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>137498784</v>
       </c>
       <c r="B17" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>137498785</v>
       </c>
       <c r="B18" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>137498786</v>
       </c>
       <c r="B19" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>137498787</v>
       </c>
       <c r="B20" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>137498789</v>
       </c>
       <c r="B21" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>137498791</v>
       </c>
       <c r="B22" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>137498801</v>
       </c>
       <c r="B23" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>137498803</v>
       </c>
       <c r="B24" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>137498811</v>
       </c>
       <c r="B25" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>137498812</v>
       </c>
       <c r="B26" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>137498800</v>
       </c>
       <c r="B27" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
